--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/54.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/54.xlsx
@@ -426,13 +426,13 @@
         <v>-6.772958932287405</v>
       </c>
       <c r="E2">
-        <v>-15.17964167480097</v>
+        <v>-14.31607073848625</v>
       </c>
       <c r="F2">
-        <v>-0.1330815123442623</v>
+        <v>0.8437657772026379</v>
       </c>
       <c r="G2">
-        <v>-13.92055510958865</v>
+        <v>-14.07369464160027</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.382257727633187</v>
       </c>
       <c r="E3">
-        <v>-14.82700940382368</v>
+        <v>-13.69751288835653</v>
       </c>
       <c r="F3">
-        <v>0.3813271894876055</v>
+        <v>0.772812795683249</v>
       </c>
       <c r="G3">
-        <v>-14.45314494639914</v>
+        <v>-14.40212031053899</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.943659220007839</v>
       </c>
       <c r="E4">
-        <v>-15.88486093201547</v>
+        <v>-15.50303358911073</v>
       </c>
       <c r="F4">
-        <v>0.4413101014917205</v>
+        <v>1.364616692326077</v>
       </c>
       <c r="G4">
-        <v>-15.03375053889976</v>
+        <v>-14.99889904410612</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.492948953486738</v>
       </c>
       <c r="E5">
-        <v>-16.45027713966518</v>
+        <v>-15.66189698577382</v>
       </c>
       <c r="F5">
-        <v>0.5964185841963167</v>
+        <v>0.6554397616457814</v>
       </c>
       <c r="G5">
-        <v>-14.53896529628641</v>
+        <v>-14.48597684932294</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.032102050374735</v>
       </c>
       <c r="E6">
-        <v>-17.5133952831279</v>
+        <v>-16.4394269159428</v>
       </c>
       <c r="F6">
-        <v>0.5450084464437738</v>
+        <v>1.291327714730794</v>
       </c>
       <c r="G6">
-        <v>-14.7848518368973</v>
+        <v>-13.50186467616038</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.580481695471826</v>
       </c>
       <c r="E7">
-        <v>-17.17575678959</v>
+        <v>-16.69805259499486</v>
       </c>
       <c r="F7">
-        <v>0.6811282631739969</v>
+        <v>1.646450477045748</v>
       </c>
       <c r="G7">
-        <v>-14.49071493325478</v>
+        <v>-12.47078017576359</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.14987128742334</v>
       </c>
       <c r="E8">
-        <v>-18.79805090351985</v>
+        <v>-15.94921960461249</v>
       </c>
       <c r="F8">
-        <v>0.7303175479196344</v>
+        <v>1.307747613389086</v>
       </c>
       <c r="G8">
-        <v>-13.78843836410839</v>
+        <v>-13.28838183905979</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.754336432821043</v>
       </c>
       <c r="E9">
-        <v>-19.08962575945172</v>
+        <v>-17.71086844918038</v>
       </c>
       <c r="F9">
-        <v>0.5589830045290014</v>
+        <v>1.3862238276607</v>
       </c>
       <c r="G9">
-        <v>-13.2434291036954</v>
+        <v>-12.01623583435528</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.402848906122919</v>
       </c>
       <c r="E10">
-        <v>-18.86826489300878</v>
+        <v>-19.1800548569109</v>
       </c>
       <c r="F10">
-        <v>0.6143809029586211</v>
+        <v>1.768845074278986</v>
       </c>
       <c r="G10">
-        <v>-12.33711633431805</v>
+        <v>-12.5468487351762</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.104095327377555</v>
       </c>
       <c r="E11">
-        <v>-19.15216851397166</v>
+        <v>-18.84680445468643</v>
       </c>
       <c r="F11">
-        <v>0.2107497739031313</v>
+        <v>2.280426558165099</v>
       </c>
       <c r="G11">
-        <v>-11.83810159711458</v>
+        <v>-11.80933512770293</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.863335187383593</v>
       </c>
       <c r="E12">
-        <v>-20.54066657183351</v>
+        <v>-22.02264139016168</v>
       </c>
       <c r="F12">
-        <v>0.2181330125642833</v>
+        <v>1.613590798911497</v>
       </c>
       <c r="G12">
-        <v>-11.30868634216286</v>
+        <v>-12.13322450783572</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.680916130025783</v>
       </c>
       <c r="E13">
-        <v>-21.60895170413897</v>
+        <v>-21.34132341875966</v>
       </c>
       <c r="F13">
-        <v>1.278461512230512</v>
+        <v>1.470659317028053</v>
       </c>
       <c r="G13">
-        <v>-11.14157372814034</v>
+        <v>-9.459097842541023</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.562560302187884</v>
       </c>
       <c r="E14">
-        <v>-22.39351888291588</v>
+        <v>-20.61589358204893</v>
       </c>
       <c r="F14">
-        <v>0.8199054825324009</v>
+        <v>1.126409705242246</v>
       </c>
       <c r="G14">
-        <v>-10.14274691689445</v>
+        <v>-9.756074643443245</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.508668970427435</v>
       </c>
       <c r="E15">
-        <v>-22.35973646681866</v>
+        <v>-24.66967935881326</v>
       </c>
       <c r="F15">
-        <v>1.106131271221714</v>
+        <v>2.176764661378769</v>
       </c>
       <c r="G15">
-        <v>-9.723997421478115</v>
+        <v>-7.700911050679084</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.517199932614984</v>
       </c>
       <c r="E16">
-        <v>-24.15341520804281</v>
+        <v>-22.89953509700698</v>
       </c>
       <c r="F16">
-        <v>0.8814134189250699</v>
+        <v>1.812447020892741</v>
       </c>
       <c r="G16">
-        <v>-9.051878559684578</v>
+        <v>-8.273756554191619</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.583902701582367</v>
       </c>
       <c r="E17">
-        <v>-23.01659162163125</v>
+        <v>-23.88996217569856</v>
       </c>
       <c r="F17">
-        <v>0.5815402772746348</v>
+        <v>2.011185614702787</v>
       </c>
       <c r="G17">
-        <v>-8.462213514458327</v>
+        <v>-8.142258318975314</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.702659306729472</v>
       </c>
       <c r="E18">
-        <v>-24.75788044706065</v>
+        <v>-24.39402208901835</v>
       </c>
       <c r="F18">
-        <v>1.29109577185801</v>
+        <v>2.336743944411826</v>
       </c>
       <c r="G18">
-        <v>-8.074740622946619</v>
+        <v>-8.804166019275858</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.86524245162279</v>
       </c>
       <c r="E19">
-        <v>-25.17959458902495</v>
+        <v>-23.50479734745017</v>
       </c>
       <c r="F19">
-        <v>0.8136612490500983</v>
+        <v>1.566610770029126</v>
       </c>
       <c r="G19">
-        <v>-7.676945008408899</v>
+        <v>-8.498175702749842</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.060400174134585</v>
       </c>
       <c r="E20">
-        <v>-25.83255525619094</v>
+        <v>-25.07353772776531</v>
       </c>
       <c r="F20">
-        <v>1.173487481478148</v>
+        <v>2.743833507374004</v>
       </c>
       <c r="G20">
-        <v>-7.000219311545902</v>
+        <v>-6.715714433791129</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.281762189401695</v>
       </c>
       <c r="E21">
-        <v>-25.62389223086551</v>
+        <v>-27.64980923309902</v>
       </c>
       <c r="F21">
-        <v>1.41313582784285</v>
+        <v>3.535189454616428</v>
       </c>
       <c r="G21">
-        <v>-7.646590427762476</v>
+        <v>-5.983017659567124</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.52015093990675</v>
       </c>
       <c r="E22">
-        <v>-26.6163254235425</v>
+        <v>-28.40452018274335</v>
       </c>
       <c r="F22">
-        <v>1.253053827251846</v>
+        <v>2.366906458282562</v>
       </c>
       <c r="G22">
-        <v>-6.679529122433573</v>
+        <v>-6.334141178643303</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.766993070454024</v>
       </c>
       <c r="E23">
-        <v>-27.21937325019594</v>
+        <v>-27.5154267669214</v>
       </c>
       <c r="F23">
-        <v>1.016238497404717</v>
+        <v>3.013566501073579</v>
       </c>
       <c r="G23">
-        <v>-6.237236862328222</v>
+        <v>-7.254002111839594</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.014222568912892</v>
       </c>
       <c r="E24">
-        <v>-28.50501607792157</v>
+        <v>-27.01585004286921</v>
       </c>
       <c r="F24">
-        <v>1.679651442549952</v>
+        <v>2.925181355929677</v>
       </c>
       <c r="G24">
-        <v>-6.190735390387772</v>
+        <v>-6.271857031001923</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.254087036708829</v>
       </c>
       <c r="E25">
-        <v>-27.9591040078229</v>
+        <v>-25.83321641339606</v>
       </c>
       <c r="F25">
-        <v>1.749671682373788</v>
+        <v>3.262929940338314</v>
       </c>
       <c r="G25">
-        <v>-5.893912806898843</v>
+        <v>-6.443510855662714</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.478013032347439</v>
       </c>
       <c r="E26">
-        <v>-28.56573838589042</v>
+        <v>-27.78407395895244</v>
       </c>
       <c r="F26">
-        <v>1.062388502149483</v>
+        <v>3.526541298931201</v>
       </c>
       <c r="G26">
-        <v>-5.828078377530145</v>
+        <v>-4.77912434452062</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.678475428326227</v>
       </c>
       <c r="E27">
-        <v>-27.99131957191347</v>
+        <v>-26.16510374494421</v>
       </c>
       <c r="F27">
-        <v>1.599725585323439</v>
+        <v>4.026048499554109</v>
       </c>
       <c r="G27">
-        <v>-6.138281782538488</v>
+        <v>-7.609709497434317</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.851678693826083</v>
       </c>
       <c r="E28">
-        <v>-28.61684221506698</v>
+        <v>-29.84240124965884</v>
       </c>
       <c r="F28">
-        <v>1.657872006795547</v>
+        <v>3.38034107927631</v>
       </c>
       <c r="G28">
-        <v>-5.320007468822606</v>
+        <v>-5.374885899404319</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.993185760900504</v>
       </c>
       <c r="E29">
-        <v>-27.6165611769347</v>
+        <v>-28.57337339306736</v>
       </c>
       <c r="F29">
-        <v>1.359272065843215</v>
+        <v>3.443598527623692</v>
       </c>
       <c r="G29">
-        <v>-5.530645486831159</v>
+        <v>-4.928114771870327</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.099892006650758</v>
       </c>
       <c r="E30">
-        <v>-26.95855126125016</v>
+        <v>-28.25537489130073</v>
       </c>
       <c r="F30">
-        <v>1.860838587829482</v>
+        <v>3.245057085255512</v>
       </c>
       <c r="G30">
-        <v>-6.180160013301681</v>
+        <v>-5.759979905285429</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.170223843835408</v>
       </c>
       <c r="E31">
-        <v>-27.55261006699838</v>
+        <v>-27.97901570803463</v>
       </c>
       <c r="F31">
-        <v>1.870083168044725</v>
+        <v>2.430690748298124</v>
       </c>
       <c r="G31">
-        <v>-5.29658282810973</v>
+        <v>-5.508300368011341</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.203767226425483</v>
       </c>
       <c r="E32">
-        <v>-28.28514960790116</v>
+        <v>-26.26851597738337</v>
       </c>
       <c r="F32">
-        <v>1.319073052520161</v>
+        <v>3.426274051761543</v>
       </c>
       <c r="G32">
-        <v>-5.761902701119263</v>
+        <v>-6.334311802164394</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.199249710051073</v>
       </c>
       <c r="E33">
-        <v>-28.02864325468469</v>
+        <v>-26.48340112599535</v>
       </c>
       <c r="F33">
-        <v>1.549806508895935</v>
+        <v>3.751560676962464</v>
       </c>
       <c r="G33">
-        <v>-6.44365522941133</v>
+        <v>-5.081009852875772</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.159982868139361</v>
       </c>
       <c r="E34">
-        <v>-27.00586928615631</v>
+        <v>-25.44152605410261</v>
       </c>
       <c r="F34">
-        <v>1.385074053705614</v>
+        <v>2.737236389378109</v>
       </c>
       <c r="G34">
-        <v>-6.500246457647073</v>
+        <v>-6.081470712458263</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.089889289678409</v>
       </c>
       <c r="E35">
-        <v>-26.52876737860419</v>
+        <v>-26.91103398348768</v>
       </c>
       <c r="F35">
-        <v>1.680488093626779</v>
+        <v>3.317201259100127</v>
       </c>
       <c r="G35">
-        <v>-6.484923152964466</v>
+        <v>-8.129891394917767</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.99234772943024</v>
       </c>
       <c r="E36">
-        <v>-25.64434734795815</v>
+        <v>-26.67169054676027</v>
       </c>
       <c r="F36">
-        <v>1.145043001600818</v>
+        <v>3.30764189927182</v>
       </c>
       <c r="G36">
-        <v>-6.27571902877739</v>
+        <v>-7.08390686741954</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.871087522725695</v>
       </c>
       <c r="E37">
-        <v>-25.72906151121964</v>
+        <v>-26.78152868381632</v>
       </c>
       <c r="F37">
-        <v>1.74968990645665</v>
+        <v>3.755878127865855</v>
       </c>
       <c r="G37">
-        <v>-6.470216717935035</v>
+        <v>-6.766573367962522</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.730349947434243</v>
       </c>
       <c r="E38">
-        <v>-25.24364079691544</v>
+        <v>-24.31171254545493</v>
       </c>
       <c r="F38">
-        <v>1.819219752778029</v>
+        <v>3.071698011932437</v>
       </c>
       <c r="G38">
-        <v>-7.435568506831467</v>
+        <v>-8.451398608198398</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.575172576177972</v>
       </c>
       <c r="E39">
-        <v>-25.18463478059549</v>
+        <v>-25.18208072125516</v>
       </c>
       <c r="F39">
-        <v>1.834625729735295</v>
+        <v>4.13958784925142</v>
       </c>
       <c r="G39">
-        <v>-7.349029569422672</v>
+        <v>-9.357412786413832</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.408959192615486</v>
       </c>
       <c r="E40">
-        <v>-23.12385305697692</v>
+        <v>-24.3741556735467</v>
       </c>
       <c r="F40">
-        <v>1.639367935751812</v>
+        <v>3.707211542951384</v>
       </c>
       <c r="G40">
-        <v>-7.554735911427381</v>
+        <v>-8.032914891728378</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.242474117113776</v>
       </c>
       <c r="E41">
-        <v>-25.20311548302079</v>
+        <v>-22.87663007547618</v>
       </c>
       <c r="F41">
-        <v>2.380667297577867</v>
+        <v>3.761009035558795</v>
       </c>
       <c r="G41">
-        <v>-8.341428467633607</v>
+        <v>-7.98769637741767</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.084653443808878</v>
       </c>
       <c r="E42">
-        <v>-23.62645027319223</v>
+        <v>-23.60181990306451</v>
       </c>
       <c r="F42">
-        <v>1.746520572773539</v>
+        <v>3.386088292316933</v>
       </c>
       <c r="G42">
-        <v>-8.519795671605022</v>
+        <v>-8.731470555626361</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.944438839605941</v>
       </c>
       <c r="E43">
-        <v>-22.55375893567729</v>
+        <v>-22.94107478907933</v>
       </c>
       <c r="F43">
-        <v>1.909029689854746</v>
+        <v>3.300826092281586</v>
       </c>
       <c r="G43">
-        <v>-8.735224273090365</v>
+        <v>-8.524281101476783</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.830406316309942</v>
       </c>
       <c r="E44">
-        <v>-22.11905713025899</v>
+        <v>-25.3067314967903</v>
       </c>
       <c r="F44">
-        <v>2.428722547349072</v>
+        <v>2.975395331152578</v>
       </c>
       <c r="G44">
-        <v>-8.457747771915923</v>
+        <v>-9.2948497349399</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.750274097585849</v>
       </c>
       <c r="E45">
-        <v>-21.74478328199905</v>
+        <v>-23.6346422826721</v>
       </c>
       <c r="F45">
-        <v>2.679494211198566</v>
+        <v>2.85359550171455</v>
       </c>
       <c r="G45">
-        <v>-9.000642285033848</v>
+        <v>-10.31666806565282</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.709452208721135</v>
       </c>
       <c r="E46">
-        <v>-21.72363077990922</v>
+        <v>-18.7885139372597</v>
       </c>
       <c r="F46">
-        <v>2.689441246971383</v>
+        <v>4.086824159162703</v>
       </c>
       <c r="G46">
-        <v>-8.580659050311162</v>
+        <v>-9.78589438497548</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.710362096493277</v>
       </c>
       <c r="E47">
-        <v>-21.46256878184103</v>
+        <v>-20.0883671164214</v>
       </c>
       <c r="F47">
-        <v>2.256211722246463</v>
+        <v>3.113205845751915</v>
       </c>
       <c r="G47">
-        <v>-8.357883793754223</v>
+        <v>-9.568529862770065</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.758520871056585</v>
       </c>
       <c r="E48">
-        <v>-18.90414852104556</v>
+        <v>-19.90136378227465</v>
       </c>
       <c r="F48">
-        <v>2.690837874412503</v>
+        <v>3.436847333290876</v>
       </c>
       <c r="G48">
-        <v>-9.990688547386663</v>
+        <v>-8.489290154766865</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.853607054908207</v>
       </c>
       <c r="E49">
-        <v>-20.59458258336883</v>
+        <v>-19.74138185253167</v>
       </c>
       <c r="F49">
-        <v>2.328838005919508</v>
+        <v>3.082897539218286</v>
       </c>
       <c r="G49">
-        <v>-9.180305571521243</v>
+        <v>-9.82099361199686</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.992226684188608</v>
       </c>
       <c r="E50">
-        <v>-19.86575639115234</v>
+        <v>-20.43978575636464</v>
       </c>
       <c r="F50">
-        <v>2.710299538173874</v>
+        <v>4.460426141499307</v>
       </c>
       <c r="G50">
-        <v>-9.071316516202728</v>
+        <v>-9.902823996467852</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.168396212005752</v>
       </c>
       <c r="E51">
-        <v>-17.58965931389107</v>
+        <v>-19.34469658640777</v>
       </c>
       <c r="F51">
-        <v>2.654021913562481</v>
+        <v>3.820035183212677</v>
       </c>
       <c r="G51">
-        <v>-9.718691686216493</v>
+        <v>-10.34926372062434</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.374419843648222</v>
       </c>
       <c r="E52">
-        <v>-17.6668969665659</v>
+        <v>-18.06772125793282</v>
       </c>
       <c r="F52">
-        <v>3.078888240988737</v>
+        <v>4.345042845963365</v>
       </c>
       <c r="G52">
-        <v>-9.211450926563494</v>
+        <v>-9.380611022839107</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.599528475477448</v>
       </c>
       <c r="E53">
-        <v>-17.20870596646981</v>
+        <v>-17.86809706672669</v>
       </c>
       <c r="F53">
-        <v>2.46308157048239</v>
+        <v>3.658727198865529</v>
       </c>
       <c r="G53">
-        <v>-10.11650042564045</v>
+        <v>-10.40647838095638</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.834335756152338</v>
       </c>
       <c r="E54">
-        <v>-15.82357709326967</v>
+        <v>-16.03435491595669</v>
       </c>
       <c r="F54">
-        <v>2.569127508653977</v>
+        <v>3.579064762473106</v>
       </c>
       <c r="G54">
-        <v>-10.00779683659761</v>
+        <v>-10.0709701952816</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.0724178435888</v>
       </c>
       <c r="E55">
-        <v>-16.60876014451162</v>
+        <v>-13.84042247109059</v>
       </c>
       <c r="F55">
-        <v>2.639550335035574</v>
+        <v>3.207767298251089</v>
       </c>
       <c r="G55">
-        <v>-9.48671260318531</v>
+        <v>-10.26923144556792</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.30591069995589</v>
       </c>
       <c r="E56">
-        <v>-16.49589245834444</v>
+        <v>-16.81325697375</v>
       </c>
       <c r="F56">
-        <v>2.464479854658316</v>
+        <v>2.435945911101484</v>
       </c>
       <c r="G56">
-        <v>-9.634771163612134</v>
+        <v>-10.70195894482749</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.527895045153516</v>
       </c>
       <c r="E57">
-        <v>-15.20527283768438</v>
+        <v>-15.62838627811706</v>
       </c>
       <c r="F57">
-        <v>2.444115270427893</v>
+        <v>3.277486012340307</v>
       </c>
       <c r="G57">
-        <v>-10.7867489911451</v>
+        <v>-10.59149333980723</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.732424403939192</v>
       </c>
       <c r="E58">
-        <v>-14.32630508974358</v>
+        <v>-14.27059580250122</v>
       </c>
       <c r="F58">
-        <v>2.15978644309099</v>
+        <v>3.238352279497253</v>
       </c>
       <c r="G58">
-        <v>-9.865595256654391</v>
+        <v>-10.59802625193208</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.91462286810283</v>
       </c>
       <c r="E59">
-        <v>-15.25388147768272</v>
+        <v>-15.28122893221504</v>
       </c>
       <c r="F59">
-        <v>2.401938115746953</v>
+        <v>3.510628361123422</v>
       </c>
       <c r="G59">
-        <v>-11.12276248494004</v>
+        <v>-10.01116008869604</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.067812350242716</v>
       </c>
       <c r="E60">
-        <v>-14.97303004820101</v>
+        <v>-14.41407144448624</v>
       </c>
       <c r="F60">
-        <v>1.988122209474043</v>
+        <v>3.025125539812243</v>
       </c>
       <c r="G60">
-        <v>-11.15955482228609</v>
+        <v>-10.7581728325839</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.19168375229933</v>
       </c>
       <c r="E61">
-        <v>-13.67490674611024</v>
+        <v>-13.04555301394624</v>
       </c>
       <c r="F61">
-        <v>2.129560973297642</v>
+        <v>3.566556414690834</v>
       </c>
       <c r="G61">
-        <v>-10.34908981588169</v>
+        <v>-10.57529066774669</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.286746945191434</v>
       </c>
       <c r="E62">
-        <v>-13.16854183952056</v>
+        <v>-13.34509798413161</v>
       </c>
       <c r="F62">
-        <v>2.03502105835094</v>
+        <v>3.150026776806353</v>
       </c>
       <c r="G62">
-        <v>-10.76820024566956</v>
+        <v>-10.1768125591246</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.353746542745644</v>
       </c>
       <c r="E63">
-        <v>-13.96527702795607</v>
+        <v>-12.90276570001038</v>
       </c>
       <c r="F63">
-        <v>2.185861792196313</v>
+        <v>2.982365214479733</v>
       </c>
       <c r="G63">
-        <v>-10.65619246651636</v>
+        <v>-10.94766665886339</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.394639239364602</v>
       </c>
       <c r="E64">
-        <v>-11.73958186640018</v>
+        <v>-10.93831820395699</v>
       </c>
       <c r="F64">
-        <v>2.006984135235788</v>
+        <v>3.831527952559117</v>
       </c>
       <c r="G64">
-        <v>-10.58143311450597</v>
+        <v>-11.10543435388461</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.412483198586421</v>
       </c>
       <c r="E65">
-        <v>-12.56053986230272</v>
+        <v>-13.71752421499643</v>
       </c>
       <c r="F65">
-        <v>2.142203516599168</v>
+        <v>3.173086868565485</v>
       </c>
       <c r="G65">
-        <v>-10.74665246368869</v>
+        <v>-10.84459364601656</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.41098858640756</v>
       </c>
       <c r="E66">
-        <v>-12.07935779966969</v>
+        <v>-12.33368595688847</v>
       </c>
       <c r="F66">
-        <v>1.765722129170432</v>
+        <v>2.997260917116873</v>
       </c>
       <c r="G66">
-        <v>-10.525022353456</v>
+        <v>-10.55595114787532</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.390734708935603</v>
       </c>
       <c r="E67">
-        <v>-11.75031434979835</v>
+        <v>-12.49576004162299</v>
       </c>
       <c r="F67">
-        <v>1.66670240330939</v>
+        <v>2.576011241771241</v>
       </c>
       <c r="G67">
-        <v>-10.45383625172384</v>
+        <v>-11.62474016521169</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.36078554661897</v>
       </c>
       <c r="E68">
-        <v>-11.76352390847873</v>
+        <v>-11.88879961342692</v>
       </c>
       <c r="F68">
-        <v>1.819566010352399</v>
+        <v>2.580365140840355</v>
       </c>
       <c r="G68">
-        <v>-10.17449601670364</v>
+        <v>-10.53524992105678</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.326461151881665</v>
       </c>
       <c r="E69">
-        <v>-12.50203197812362</v>
+        <v>-11.96197069644286</v>
       </c>
       <c r="F69">
-        <v>1.661579779290478</v>
+        <v>2.996121083570621</v>
       </c>
       <c r="G69">
-        <v>-10.86412347673837</v>
+        <v>-11.57361545209398</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.292344604535026</v>
       </c>
       <c r="E70">
-        <v>-12.16060768031531</v>
+        <v>-12.69571933990569</v>
       </c>
       <c r="F70">
-        <v>1.812170346180205</v>
+        <v>3.286422439881708</v>
       </c>
       <c r="G70">
-        <v>-9.769242185561298</v>
+        <v>-9.03963632204629</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.262495105734827</v>
       </c>
       <c r="E71">
-        <v>-11.98759280237826</v>
+        <v>-11.81863090867807</v>
       </c>
       <c r="F71">
-        <v>1.070420352487027</v>
+        <v>2.662337065551783</v>
       </c>
       <c r="G71">
-        <v>-8.619840116952492</v>
+        <v>-9.256223194742116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.240132729201024</v>
       </c>
       <c r="E72">
-        <v>-11.77391222785232</v>
+        <v>-11.66300084245646</v>
       </c>
       <c r="F72">
-        <v>1.186356997448041</v>
+        <v>2.656255192080429</v>
       </c>
       <c r="G72">
-        <v>-9.534178754264238</v>
+        <v>-10.71669819207252</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.226613214492859</v>
       </c>
       <c r="E73">
-        <v>-12.80853721285878</v>
+        <v>-12.03120200707212</v>
       </c>
       <c r="F73">
-        <v>1.329286822596679</v>
+        <v>2.29176856464423</v>
       </c>
       <c r="G73">
-        <v>-8.780321382203374</v>
+        <v>-10.67170608204941</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.221732328762833</v>
       </c>
       <c r="E74">
-        <v>-12.51948018847517</v>
+        <v>-12.22286514097276</v>
       </c>
       <c r="F74">
-        <v>1.327436249818824</v>
+        <v>2.909909574491666</v>
       </c>
       <c r="G74">
-        <v>-8.799555902984839</v>
+        <v>-10.2483267830127</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.231686761366102</v>
       </c>
       <c r="E75">
-        <v>-11.43270982527039</v>
+        <v>-12.33619020301471</v>
       </c>
       <c r="F75">
-        <v>0.8933187152381042</v>
+        <v>1.840555183604533</v>
       </c>
       <c r="G75">
-        <v>-8.519362550359176</v>
+        <v>-10.0231693596036</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.258073960857756</v>
       </c>
       <c r="E76">
-        <v>-11.72149966968755</v>
+        <v>-11.04349201278513</v>
       </c>
       <c r="F76">
-        <v>0.6573400364678035</v>
+        <v>2.318738550544576</v>
       </c>
       <c r="G76">
-        <v>-8.503051597987175</v>
+        <v>-9.425232354825996</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.302210938762746</v>
       </c>
       <c r="E77">
-        <v>-12.81102334508899</v>
+        <v>-13.65330139661964</v>
       </c>
       <c r="F77">
-        <v>0.2191336803868651</v>
+        <v>2.144673708194316</v>
       </c>
       <c r="G77">
-        <v>-8.38774619116673</v>
+        <v>-8.038630779684931</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.365404339562192</v>
       </c>
       <c r="E78">
-        <v>-12.57773900658385</v>
+        <v>-13.43750149625812</v>
       </c>
       <c r="F78">
-        <v>0.9796594496318968</v>
+        <v>2.244896223524222</v>
       </c>
       <c r="G78">
-        <v>-8.89882269882272</v>
+        <v>-9.288428384348066</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.448513512939722</v>
       </c>
       <c r="E79">
-        <v>-13.31013363631839</v>
+        <v>-14.11077689782252</v>
       </c>
       <c r="F79">
-        <v>0.8367080869307861</v>
+        <v>2.405703873960079</v>
       </c>
       <c r="G79">
-        <v>-6.556860654433732</v>
+        <v>-9.617649749514952</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.549185360901621</v>
       </c>
       <c r="E80">
-        <v>-13.67223041797171</v>
+        <v>-13.94969907736968</v>
       </c>
       <c r="F80">
-        <v>0.5486540913834944</v>
+        <v>2.089888801642768</v>
       </c>
       <c r="G80">
-        <v>-6.62719035733887</v>
+        <v>-8.373577876473048</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.668480210430317</v>
       </c>
       <c r="E81">
-        <v>-14.45953732352325</v>
+        <v>-14.066782772838</v>
       </c>
       <c r="F81">
-        <v>0.1925190641023198</v>
+        <v>2.355584332621098</v>
       </c>
       <c r="G81">
-        <v>-6.543217335189561</v>
+        <v>-7.846961503511527</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.809768147827273</v>
       </c>
       <c r="E82">
-        <v>-15.13873144061568</v>
+        <v>-13.82458639748577</v>
       </c>
       <c r="F82">
-        <v>-0.05770007868950731</v>
+        <v>2.268320796940587</v>
       </c>
       <c r="G82">
-        <v>-6.820431338639247</v>
+        <v>-8.615105314242212</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.973288544660053</v>
       </c>
       <c r="E83">
-        <v>-15.74246759531829</v>
+        <v>-14.98041146083351</v>
       </c>
       <c r="F83">
-        <v>0.2751893025343076</v>
+        <v>2.058304809308828</v>
       </c>
       <c r="G83">
-        <v>-6.934529255925819</v>
+        <v>-9.09636864280909</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.158506308989407</v>
       </c>
       <c r="E84">
-        <v>-16.82375397649978</v>
+        <v>-16.32462104290034</v>
       </c>
       <c r="F84">
-        <v>-0.06176239243283609</v>
+        <v>1.630159803702293</v>
       </c>
       <c r="G84">
-        <v>-5.52278696119629</v>
+        <v>-7.270434469409293</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.363893610029326</v>
       </c>
       <c r="E85">
-        <v>-17.4177539120859</v>
+        <v>-16.17734601122289</v>
       </c>
       <c r="F85">
-        <v>-0.1359882535606858</v>
+        <v>2.245134793336229</v>
       </c>
       <c r="G85">
-        <v>-5.612452902751235</v>
+        <v>-6.418553884481578</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.587352860251945</v>
       </c>
       <c r="E86">
-        <v>-18.41310797049784</v>
+        <v>-18.34084711075744</v>
       </c>
       <c r="F86">
-        <v>-0.3411342692313862</v>
+        <v>0.4864909163752111</v>
       </c>
       <c r="G86">
-        <v>-5.964360633780121</v>
+        <v>-7.027761885315881</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.82029856663858</v>
       </c>
       <c r="E87">
-        <v>-19.53940285484156</v>
+        <v>-20.17791316144907</v>
       </c>
       <c r="F87">
-        <v>-0.3206760794844468</v>
+        <v>1.698027945013656</v>
       </c>
       <c r="G87">
-        <v>-5.167351916991</v>
+        <v>-6.684063770628725</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.062989109576241</v>
       </c>
       <c r="E88">
-        <v>-20.2000664562946</v>
+        <v>-20.95046629868363</v>
       </c>
       <c r="F88">
-        <v>-0.4171750833387696</v>
+        <v>2.021558431320642</v>
       </c>
       <c r="G88">
-        <v>-5.147697399849926</v>
+        <v>-9.15261534278109</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.313259898377433</v>
       </c>
       <c r="E89">
-        <v>-23.40700495125453</v>
+        <v>-20.63770271286987</v>
       </c>
       <c r="F89">
-        <v>-0.9491609130906401</v>
+        <v>0.9981138186314642</v>
       </c>
       <c r="G89">
-        <v>-5.62371405514325</v>
+        <v>-6.074140463494463</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.567734529512691</v>
       </c>
       <c r="E90">
-        <v>-23.30122432690936</v>
+        <v>-24.78747855317478</v>
       </c>
       <c r="F90">
-        <v>-1.292398259910226</v>
+        <v>0.8955785015129414</v>
       </c>
       <c r="G90">
-        <v>-5.711312827115745</v>
+        <v>-6.837070413167192</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.823475419985334</v>
       </c>
       <c r="E91">
-        <v>-24.19693837173052</v>
+        <v>-23.81005725183322</v>
       </c>
       <c r="F91">
-        <v>-0.9990079215541003</v>
+        <v>1.035451650945249</v>
       </c>
       <c r="G91">
-        <v>-5.034062134803237</v>
+        <v>-6.535280060237264</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.078316995162108</v>
       </c>
       <c r="E92">
-        <v>-27.49735362715679</v>
+        <v>-25.56152155835786</v>
       </c>
       <c r="F92">
-        <v>-1.094781275563571</v>
+        <v>1.020529440551219</v>
       </c>
       <c r="G92">
-        <v>-5.532046568437043</v>
+        <v>-6.596888276237398</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.3304692928359</v>
       </c>
       <c r="E93">
-        <v>-28.30021131245067</v>
+        <v>-27.63843370639175</v>
       </c>
       <c r="F93">
-        <v>-1.063671109384033</v>
+        <v>0.8333217209881417</v>
       </c>
       <c r="G93">
-        <v>-4.885754201537895</v>
+        <v>-8.406173531444571</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.572817785340554</v>
       </c>
       <c r="E94">
-        <v>-29.9197747565539</v>
+        <v>-31.16813918624839</v>
       </c>
       <c r="F94">
-        <v>-1.425728963595224</v>
+        <v>0.3397646834195431</v>
       </c>
       <c r="G94">
-        <v>-5.26591653141516</v>
+        <v>-7.410424506021442</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.812307666700061</v>
       </c>
       <c r="E95">
-        <v>-32.18278680817</v>
+        <v>-32.46793349524798</v>
       </c>
       <c r="F95">
-        <v>-1.944887524114744</v>
+        <v>0.2795481718078386</v>
       </c>
       <c r="G95">
-        <v>-5.798097856141498</v>
+        <v>-6.65980898086131</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.05032688106053</v>
       </c>
       <c r="E96">
-        <v>-34.47890200478218</v>
+        <v>-32.50568738304993</v>
       </c>
       <c r="F96">
-        <v>-1.98594803953671</v>
+        <v>-0.05313328919787364</v>
       </c>
       <c r="G96">
-        <v>-5.582196758751595</v>
+        <v>-7.149902076644651</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.28661940280212</v>
       </c>
       <c r="E97">
-        <v>-35.86364595769167</v>
+        <v>-36.30215620975041</v>
       </c>
       <c r="F97">
-        <v>-1.780549371808156</v>
+        <v>0.1636430048081318</v>
       </c>
       <c r="G97">
-        <v>-5.889571750775698</v>
+        <v>-7.831992570757341</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.5219254602035</v>
       </c>
       <c r="E98">
-        <v>-38.28336132386919</v>
+        <v>-38.9395824923207</v>
       </c>
       <c r="F98">
-        <v>-2.092321182832403</v>
+        <v>0.03460655773924719</v>
       </c>
       <c r="G98">
-        <v>-5.782679396033667</v>
+        <v>-7.472383812728437</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.75171045470088</v>
       </c>
       <c r="E99">
-        <v>-40.52921045899622</v>
+        <v>-39.0152102724858</v>
       </c>
       <c r="F99">
-        <v>-1.923047617539935</v>
+        <v>0.8248690600099755</v>
       </c>
       <c r="G99">
-        <v>-5.970982138887081</v>
+        <v>-8.512859169228356</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.97237566861014</v>
       </c>
       <c r="E100">
-        <v>-41.85192337494865</v>
+        <v>-41.2556025964336</v>
       </c>
       <c r="F100">
-        <v>-2.106381891127521</v>
+        <v>0.1575569894997638</v>
       </c>
       <c r="G100">
-        <v>-7.464617161297231</v>
+        <v>-8.48187131282096</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.16933631733547</v>
       </c>
       <c r="E101">
-        <v>-44.67290003023484</v>
+        <v>-43.64095816607792</v>
       </c>
       <c r="F101">
-        <v>-2.069700125796754</v>
+        <v>0.2765329144616484</v>
       </c>
       <c r="G101">
-        <v>-6.826045508727457</v>
+        <v>-8.727119655838537</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.34958013604214</v>
       </c>
       <c r="E102">
-        <v>-45.21705278818153</v>
+        <v>-48.37148815549653</v>
       </c>
       <c r="F102">
-        <v>-1.937485233003327</v>
+        <v>-0.7925713094698383</v>
       </c>
       <c r="G102">
-        <v>-7.928585171024274</v>
+        <v>-8.907025752721331</v>
       </c>
     </row>
   </sheetData>
